--- a/business_forms/046_service_interruption_incident_form--business_forms.xlsx
+++ b/business_forms/046_service_interruption_incident_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'organization',_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'organization', 'label': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'team',_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'team', 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'service1',_'label':_'service_1'}</t>
+          <t>service_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'service1', 'label': 'Service 1'}</t>
+          <t>Service 1</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'service2',_'label':_'service_2'}</t>
+          <t>service_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'service2', 'label': 'Service 2'}</t>
+          <t>Service 2</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'service3',_'label':_'service_3'}</t>
+          <t>service_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'service3', 'label': 'Service 3'}</t>
+          <t>Service 3</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'resolved',_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'resolved', 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ongoing',_'label':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'ongoing', 'label': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'officer1',_'label':_'officer_1'}</t>
+          <t>officer_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'officer1', 'label': 'Officer 1'}</t>
+          <t>Officer 1</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'officer2',_'label':_'officer_2'}</t>
+          <t>officer_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'officer2', 'label': 'Officer 2'}</t>
+          <t>Officer 2</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'officer3',_'label':_'officer_3'}</t>
+          <t>officer_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'officer3', 'label': 'Officer 3'}</t>
+          <t>Officer 3</t>
         </is>
       </c>
     </row>
